--- a/04_DESIGN_TABLES/DesignTable_6420.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6420.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,7 +488,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled | OMi answer 2026-10-18 (staged, not shipped): OMi real Overall Length = 1.5 (Lengths to check!E16; website file said 1.320, = the row above). Still no geometry source (6420 has no Air-Way series and no generator SPEC) -&gt; stays MISSING</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_6420.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6420.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +458,46 @@
           <t>$COMMENT</t>
         </is>
       </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>L@DRIVE</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>C4HEX@HEX</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>D3@BORE</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>TAPDRILL@BORE</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>THDMAJ_B@DRIVE</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>THDMAJ_A@DRIVE</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>$PRP@Threads</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -473,7 +517,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions | 2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): L@DRIVE = OMi answer 2026-10-18 (tools/_out/omi_answers_20261018, "Lengths to check"!E16: real Overall Length 1.5; website file 1.320 = copy-down) = Brennan TFA catalog p.17 table 6420 "FORB-FP STRAIGHT" (catalog_verified.json TFA-p017-t01) "L LGTH" 1.500; C4HEX@HEX = OMi WebsitePartsInfo2026.xlsx Items!R1889 Hex Flat 1.000 = Brennan TFA catalog p.17 table 6420 "FORB-FP STRAIGHT" (catalog_verified.json TFA-p017-t01) "C4 HEX" 1.000 (OMi file = Brennan data: one source); D3@BORE = end library: female ORB -08 port drill = Air-Way 6404-08-08 D3 0.68 (Q-TRANSFER-ENDLIB = yes 2026-10-08); TAPDRILL@BORE = end library: -08 NPTF tap drill = Air-Way per size (6405-08-08-O TAPDRILL 0.70, 5000-08-08 0.70; A1 2026-10-18); THDMAJ_B@DRIVE = SAE J1926 -08 = 3/4-16 UN (= OMi Side 1 Thread "3/4-16 UNF", catalog "B SAE ORB"); THDMAJ_A@DRIVE = ASME B1.20.1 1/2 NPT pipe OD 0.840 (= OMi Side 2 Thread "1/2-14 NPTF", catalog "A NPTF")</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -488,7 +532,35 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled | OMi answer 2026-10-18 (staged, not shipped): OMi real Overall Length = 1.5 (Lengths to check!E16; website file said 1.320, = the row above). Still no geometry source (6420 has no Air-Way series and no generator SPEC) -&gt; stays MISSING</t>
+          <t>2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): dimension cells staged, DataStatus stays MISSING - NOT buildable without a user decision: at OMi's length 1.5 (= Brennan catalog 1.500) the library ports overlap - female ORB -08 port 0.688 deep (ORBF_MEAS, Brennan 6404 / 6410 STEPs) + female NPTF -08 tap drill 0.900 deep (MS51503 P1 max, Brennan 5405-08-08) = 1.588 &gt; 1.5: the 0.70 tap drill would run 0.088 into the ORB port (minor 0.68). The own Brennan STEP 09_STEP_FILES/BRENNAN_6420-08-08.stp is ANOTHER body: overall 1.620, hex 1.125 (catalog / OMi 1.500 / 1.000), with exactly the library ports (ORB face 0.813 dia, 15deg chamfer, minor 0.689 to 0.688; NPTF tapered 0.75 deep, 0.718 drill to 0.900; the two 120deg drill points meet). Options: (a) build OMi 1.5 x 1.000 with the NPTF drill shortened to meet the ORB port bottom (0.812; thread 0.75 as on the Brennan STEP) - the 5000-08-08 coupling precedent (1.5 long, drills cut to meet) - plus a new gen_straight2 bore mode (female ORB cavity + female NPTF pocket, SPEC 6420); (b) the Brennan STEP body 1.620 x 1.125 (not OMi's length). Same question as 6420-12-12 (QUESTIONS_FOR_OMi.md item 7) | was: MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled | OMi answer 2026-10-18 (staged, not shipped): OMi real Overall Length = 1.5 (Lengths to check!E16; website file said 1.320, = the row above). Still no geometry source (6420 has no Air-Way series and no generator SPEC) -&gt; stays MISSING</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3/4-16 (B, female ORB port, SAE J1926) x 1/2-14 (A, female NPTF)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
